--- a/artfynd/A 35062-2026 artfynd.xlsx
+++ b/artfynd/A 35062-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,48 +884,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80984830</v>
+        <v>137404223</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>71</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Riukka, Nb</t>
+          <t>Onttovaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>819978</v>
+        <v>819902</v>
       </c>
       <c r="R4" t="n">
-        <v>7471128</v>
+        <v>7471126</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +952,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,33 +976,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984830</t>
+          <t>https://artportalen.se/Sighting/137404223</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>80984854</v>
+        <v>137404235</v>
       </c>
       <c r="B5" t="n">
-        <v>79406</v>
+        <v>92119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,37 +1011,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Riukka, Nb</t>
+          <t>Onttovaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>819766</v>
+        <v>819746</v>
       </c>
       <c r="R5" t="n">
-        <v>7470988</v>
+        <v>7470999</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1065,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-06-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-06-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1095,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984854</t>
+          <t>https://artportalen.se/Sighting/137404235</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80984845</v>
+        <v>80984830</v>
       </c>
       <c r="B6" t="n">
-        <v>91909</v>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>819742</v>
+        <v>819978</v>
       </c>
       <c r="R6" t="n">
-        <v>7471186</v>
+        <v>7471128</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1177,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-06-26</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-06-26</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,16 +1208,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984845</t>
+          <t>https://artportalen.se/Sighting/80984830</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>80984865</v>
+        <v>80984854</v>
       </c>
       <c r="B7" t="n">
-        <v>83173</v>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1225,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>819770</v>
+        <v>819766</v>
       </c>
       <c r="R7" t="n">
-        <v>7470994</v>
+        <v>7470988</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,16 +1310,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984865</t>
+          <t>https://artportalen.se/Sighting/80984854</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>80984867</v>
+        <v>80984845</v>
       </c>
       <c r="B8" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>819761</v>
+        <v>819742</v>
       </c>
       <c r="R8" t="n">
-        <v>7470999</v>
+        <v>7471186</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,16 +1412,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984867</t>
+          <t>https://artportalen.se/Sighting/80984845</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80984843</v>
+        <v>80984865</v>
       </c>
       <c r="B9" t="n">
-        <v>92097</v>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1588</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>819737</v>
+        <v>819770</v>
       </c>
       <c r="R9" t="n">
-        <v>7471190</v>
+        <v>7470994</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,38 +1514,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984843</t>
+          <t>https://artportalen.se/Sighting/80984865</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80984833</v>
+        <v>80984867</v>
       </c>
       <c r="B10" t="n">
-        <v>79327</v>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>819967</v>
+        <v>819761</v>
       </c>
       <c r="R10" t="n">
-        <v>7471181</v>
+        <v>7470999</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,12 +1585,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-06-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-06-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,38 +1616,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984833</t>
+          <t>https://artportalen.se/Sighting/80984867</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80984858</v>
+        <v>80984843</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>92097</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>819727</v>
+        <v>819737</v>
       </c>
       <c r="R11" t="n">
-        <v>7471152</v>
+        <v>7471190</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,54 +1718,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984858</t>
+          <t>https://artportalen.se/Sighting/80984843</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>80984860</v>
+        <v>137404225</v>
       </c>
       <c r="B12" t="n">
-        <v>79327</v>
+        <v>91173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Riukka, Nb</t>
+          <t>Onttovaara, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>819766</v>
+        <v>819911</v>
       </c>
       <c r="R12" t="n">
-        <v>7470988</v>
+        <v>7471111</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1765,12 +1789,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-06-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-06-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,65 +1819,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984860</t>
+          <t>https://artportalen.se/Sighting/137404225</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80984863</v>
+        <v>137404226</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>93469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Riukka, Nb</t>
+          <t>Onttovaara, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>819704</v>
+        <v>819879</v>
       </c>
       <c r="R13" t="n">
-        <v>7471034</v>
+        <v>7471119</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1867,12 +1901,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-06-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-06-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,49 +1931,49 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984863</t>
+          <t>https://artportalen.se/Sighting/137404226</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>80984878</v>
+        <v>80984833</v>
       </c>
       <c r="B14" t="n">
-        <v>57132</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>819835</v>
+        <v>819967</v>
       </c>
       <c r="R14" t="n">
-        <v>7471013</v>
+        <v>7471181</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,12 +2013,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2019-06-26</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2019-06-26</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2000,38 +2044,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984878</t>
+          <t>https://artportalen.se/Sighting/80984833</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>80984827</v>
+        <v>80984858</v>
       </c>
       <c r="B15" t="n">
-        <v>58057</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>819825</v>
+        <v>819727</v>
       </c>
       <c r="R15" t="n">
-        <v>7471336</v>
+        <v>7471152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,12 +2115,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-06-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
+          <t>2019-06-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2102,38 +2146,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80984827</t>
+          <t>https://artportalen.se/Sighting/80984858</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80984877</v>
+        <v>80984860</v>
       </c>
       <c r="B16" t="n">
-        <v>99035</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>819835</v>
+        <v>819766</v>
       </c>
       <c r="R16" t="n">
-        <v>7471013</v>
+        <v>7470988</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,7 +2248,1439 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/80984860</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>80984863</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Riukka, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>819704</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7471034</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-06-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-06-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984863</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137404231</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79521</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>819701</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7471038</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404231</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137404228</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>819883</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7471080</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404228</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137404232</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80647</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>819707</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7471028</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404232</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137404233</v>
+      </c>
+      <c r="B21" t="n">
+        <v>83510</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>819719</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7471004</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404233</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137404234</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>819720</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7471000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404234</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137404237</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>819756</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7470987</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på 7 mm mellan hackhålen vilket är de mått som tretåig hackspett har för sina ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404237</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>80984878</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Riukka, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>819835</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7471013</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2019-06-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2019-06-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984878</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137404222</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58196</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>819905</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7471114</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404222</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>80984827</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Riukka, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>819825</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7471336</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2019-07-01</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80984827</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>80984877</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Riukka, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>819835</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7471013</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2019-06-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2019-06-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/80984877</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137404227</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79279</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>819890</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7471097</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404227</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137404229</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79279</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Onttovaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>819883</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7471080</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404229</t>
         </is>
       </c>
     </row>
@@ -2225,6 +3701,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35062-2026 artfynd.xlsx
+++ b/artfynd/A 35062-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137404223</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>137404235</v>
       </c>
       <c r="B5" t="n">
-        <v>92119</v>
+        <v>92131</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137404225</v>
       </c>
       <c r="B12" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>137404226</v>
       </c>
       <c r="B13" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>137404231</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137404228</v>
       </c>
       <c r="B19" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>137404232</v>
       </c>
       <c r="B20" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>137404233</v>
       </c>
       <c r="B21" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>137404227</v>
       </c>
       <c r="B28" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>137404229</v>
       </c>
       <c r="B29" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 35062-2026 artfynd.xlsx
+++ b/artfynd/A 35062-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137404223</v>
       </c>
       <c r="B4" t="n">
-        <v>92442</v>
+        <v>92443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>137404235</v>
       </c>
       <c r="B5" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137404225</v>
       </c>
       <c r="B12" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>137404226</v>
       </c>
       <c r="B13" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>137404231</v>
       </c>
       <c r="B18" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137404228</v>
       </c>
       <c r="B19" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>137404232</v>
       </c>
       <c r="B20" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>137404233</v>
       </c>
       <c r="B21" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>137404227</v>
       </c>
       <c r="B28" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>137404229</v>
       </c>
       <c r="B29" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 35062-2026 artfynd.xlsx
+++ b/artfynd/A 35062-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137404223</v>
       </c>
       <c r="B4" t="n">
-        <v>92443</v>
+        <v>92446</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>137404235</v>
       </c>
       <c r="B5" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137404225</v>
       </c>
       <c r="B12" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>137404226</v>
       </c>
       <c r="B13" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>137404231</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137404228</v>
       </c>
       <c r="B19" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>137404232</v>
       </c>
       <c r="B20" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>137404233</v>
       </c>
       <c r="B21" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>137404227</v>
       </c>
       <c r="B28" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>137404229</v>
       </c>
       <c r="B29" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 35062-2026 artfynd.xlsx
+++ b/artfynd/A 35062-2026 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>137404223</v>
       </c>
       <c r="B4" t="n">
-        <v>92446</v>
+        <v>92450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>137404235</v>
       </c>
       <c r="B5" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>137404225</v>
       </c>
       <c r="B12" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>137404226</v>
       </c>
       <c r="B13" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>137404231</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137404228</v>
       </c>
       <c r="B19" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>137404232</v>
       </c>
       <c r="B20" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>137404233</v>
       </c>
       <c r="B21" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>137404234</v>
       </c>
       <c r="B22" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>137404237</v>
       </c>
       <c r="B23" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>137404222</v>
       </c>
       <c r="B25" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>137404227</v>
       </c>
       <c r="B28" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>137404229</v>
       </c>
       <c r="B29" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
